--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -1,33 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>SUCURSAL</t>
+  </si>
+  <si>
+    <t>PROVEEDOR</t>
+  </si>
+  <si>
+    <t>FACTURA</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>TIPO FISCALIZACIÓN</t>
+  </si>
+  <si>
+    <t>RESPONSABLE</t>
+  </si>
+  <si>
+    <t>INCIDENCIA</t>
+  </si>
+  <si>
+    <t>TIPO DE ERROR</t>
+  </si>
+  <si>
+    <t>OBSERVACIÓN</t>
+  </si>
+  <si>
+    <t>MONTO $</t>
+  </si>
+  <si>
+    <t>F COBRADA</t>
+  </si>
+  <si>
+    <t>CLASIFICACIÓN MONTO</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>ACACIAS</t>
+  </si>
+  <si>
+    <t>YEFFERSON MAY MORGADO CHACON</t>
+  </si>
+  <si>
+    <t>124694</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>RECEPCION</t>
+  </si>
+  <si>
+    <t>SPCP DANIEL GARCIA</t>
+  </si>
+  <si>
+    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+  </si>
+  <si>
+    <t>TIPO A</t>
+  </si>
+  <si>
+    <t>NRO DE CONTROL CORRECTO: 000112694</t>
+  </si>
+  <si>
+    <t>SIN FOTO</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>20260504090310</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +125,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,84 +419,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>SUCURSAL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PROVEEDOR</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>FACTURA</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>TIPO DE FISCALIZACION</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>INCIDENCIA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>TIPO DE ERROR</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>F COBRADA</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>CLASIFICACION</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -61,7 +61,10 @@
     <t>YEFFERSON MAY MORGADO CHACON</t>
   </si>
   <si>
-    <t>124694</t>
+    <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+  </si>
+  <si>
+    <t>024717</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -73,15 +76,27 @@
     <t>SPCP DANIEL GARCIA</t>
   </si>
   <si>
+    <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
+    <t>PRODUCTO O SKU DUPLICADO.</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
+    <t>TIPO B</t>
+  </si>
+  <si>
     <t>NRO DE CONTROL CORRECTO: 000112694</t>
   </si>
   <si>
+    <t>ELIMINAR SKU RFR7505 Y AGREGAR COMPUESTO CILANTRO/CEBOLLIN 150GR</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -89,6 +104,9 @@
   </si>
   <si>
     <t>20260504090310</t>
+  </si>
+  <si>
+    <t>20260504091556</t>
   </si>
 </sst>
 </file>
@@ -420,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -471,38 +489,79 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="C2">
+        <v>124694</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="H3" t="s">
         <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -64,12 +64,27 @@
     <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
   </si>
   <si>
-    <t>024717</t>
+    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+  </si>
+  <si>
+    <t>MUSACEUM C.A</t>
+  </si>
+  <si>
+    <t>BOCADOS Y SABORES INTERNACIONALES, C.A.</t>
+  </si>
+  <si>
+    <t>31336</t>
   </si>
   <si>
     <t>2026-05-01</t>
   </si>
   <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-04</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
@@ -79,6 +94,12 @@
     <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
   </si>
   <si>
+    <t>SPCP MARWIN JARAMILLO</t>
+  </si>
+  <si>
+    <t>SPCP BRAYAN PARADA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
@@ -97,6 +118,15 @@
     <t>ELIMINAR SKU RFR7505 Y AGREGAR COMPUESTO CILANTRO/CEBOLLIN 150GR</t>
   </si>
   <si>
+    <t>NRO DE CONTROL CORRECTO: 00000848</t>
+  </si>
+  <si>
+    <t>NRO DE FACTURA CORRECTO: 004178</t>
+  </si>
+  <si>
+    <t>NRO DE CONTROL CORRECTO: 00036628</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -107,6 +137,15 @@
   </si>
   <si>
     <t>20260504091556</t>
+  </si>
+  <si>
+    <t>20260504130707</t>
+  </si>
+  <si>
+    <t>20260504131139</t>
+  </si>
+  <si>
+    <t>20260504133240</t>
   </si>
 </sst>
 </file>
@@ -438,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -493,34 +532,34 @@
         <v>124694</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -530,38 +569,161 @@
       <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
+      <c r="C3">
+        <v>24717</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>848</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>41178</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="L3" t="s">
+      <c r="G5" t="s">
         <v>28</v>
       </c>
-      <c r="M3" t="s">
+      <c r="H5" t="s">
         <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -61,19 +61,19 @@
     <t>YEFFERSON MAY MORGADO CHACON</t>
   </si>
   <si>
+    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+  </si>
+  <si>
+    <t>MUSACEUM C.A</t>
+  </si>
+  <si>
+    <t>BOCADOS Y SABORES INTERNACIONALES, C.A.</t>
+  </si>
+  <si>
     <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
   </si>
   <si>
-    <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
-  </si>
-  <si>
-    <t>MUSACEUM C.A</t>
-  </si>
-  <si>
-    <t>BOCADOS Y SABORES INTERNACIONALES, C.A.</t>
-  </si>
-  <si>
-    <t>31336</t>
+    <t>24717</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -91,15 +91,15 @@
     <t>SPCP DANIEL GARCIA</t>
   </si>
   <si>
+    <t>SPCP MARWIN JARAMILLO</t>
+  </si>
+  <si>
+    <t>SPCP BRAYAN PARADA</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
   </si>
   <si>
-    <t>SPCP MARWIN JARAMILLO</t>
-  </si>
-  <si>
-    <t>SPCP BRAYAN PARADA</t>
-  </si>
-  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
@@ -115,9 +115,6 @@
     <t>NRO DE CONTROL CORRECTO: 000112694</t>
   </si>
   <si>
-    <t>ELIMINAR SKU RFR7505 Y AGREGAR COMPUESTO CILANTRO/CEBOLLIN 150GR</t>
-  </si>
-  <si>
     <t>NRO DE CONTROL CORRECTO: 00000848</t>
   </si>
   <si>
@@ -127,6 +124,9 @@
     <t>NRO DE CONTROL CORRECTO: 00036628</t>
   </si>
   <si>
+    <t>ELIMINO EL SKU RFR7505 DUPLICADO Y AGREGO COMPUESTO CILANTRO/CEBOLLIN 150GR EN EL APLICATIVO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
@@ -136,16 +136,16 @@
     <t>20260504090310</t>
   </si>
   <si>
+    <t>20260504130707</t>
+  </si>
+  <si>
+    <t>20260504131139</t>
+  </si>
+  <si>
+    <t>20260504133240</t>
+  </si>
+  <si>
     <t>20260504091556</t>
-  </si>
-  <si>
-    <t>20260504130707</t>
-  </si>
-  <si>
-    <t>20260504131139</t>
-  </si>
-  <si>
-    <t>20260504133240</t>
   </si>
 </sst>
 </file>
@@ -570,10 +570,10 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>24717</v>
+        <v>848</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -582,10 +582,10 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
         <v>33</v>
@@ -611,7 +611,7 @@
         <v>16</v>
       </c>
       <c r="C4">
-        <v>848</v>
+        <v>41178</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -652,10 +652,10 @@
         <v>17</v>
       </c>
       <c r="C5">
-        <v>41178</v>
+        <v>31336</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -696,19 +696,19 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>36</v>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,6 +55,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>ACACIAS</t>
   </si>
   <si>
@@ -73,7 +76,10 @@
     <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
   </si>
   <si>
-    <t>24717</t>
+    <t>DISTRIBUIDORA JORIAN,C.A</t>
+  </si>
+  <si>
+    <t>32098</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -85,9 +91,15 @@
     <t>2026-05-04</t>
   </si>
   <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
     <t>RECEPCION</t>
   </si>
   <si>
+    <t>DEVOLUCION</t>
+  </si>
+  <si>
     <t>SPCP DANIEL GARCIA</t>
   </si>
   <si>
@@ -100,12 +112,18 @@
     <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
   </si>
   <si>
+    <t>SPCP OSLEN OCHOA</t>
+  </si>
+  <si>
     <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
   </si>
   <si>
     <t>PRODUCTO O SKU DUPLICADO.</t>
   </si>
   <si>
+    <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+  </si>
+  <si>
     <t>TIPO A</t>
   </si>
   <si>
@@ -127,25 +145,25 @@
     <t>ELIMINO EL SKU RFR7505 DUPLICADO Y AGREGO COMPUESTO CILANTRO/CEBOLLIN 150GR EN EL APLICATIVO</t>
   </si>
   <si>
+    <t>EL SPCP NO FIRMO EL DOCUMENTO</t>
+  </si>
+  <si>
+    <t>FALTO LA FIRMA DEL SPCP EN EL DOCUMENTO</t>
+  </si>
+  <si>
     <t>SIN FOTO</t>
   </si>
   <si>
+    <t>SIN_FOTO</t>
+  </si>
+  <si>
     <t>NINGUNA</t>
   </si>
   <si>
-    <t>20260504090310</t>
-  </si>
-  <si>
-    <t>20260504130707</t>
-  </si>
-  <si>
-    <t>20260504131139</t>
-  </si>
-  <si>
-    <t>20260504133240</t>
-  </si>
-  <si>
-    <t>20260504091556</t>
+    <t>ID_20260505090942</t>
+  </si>
+  <si>
+    <t>ID_20260505093148</t>
   </si>
 </sst>
 </file>
@@ -477,10 +495,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,210 +538,295 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>124694</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="M2">
+        <v>20260504090310</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3">
         <v>848</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>40</v>
+        <v>47</v>
+      </c>
+      <c r="M3">
+        <v>20260504130707</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>41178</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="M4">
+        <v>20260504131139</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>31336</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5">
+        <v>20260504133240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>24717</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
       </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="I6" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
+        <v>20260504091556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>32103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" t="s">
         <v>43</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L8" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -669,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -730,6 +734,7 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,6 +796,7 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -854,6 +860,7 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -917,6 +924,7 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -980,6 +988,7 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1045,6 +1054,7 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1110,8 +1120,75 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INVERSIONES RUBYMAR R.M C.A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>008771</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SUB GERENTE DIANA BENAVIDES</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>NO COLOCARON EL SELLO DE LA SUCURSAL</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260508075309</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,6 +1187,72 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADOLFO'S VICAR, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13649</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EL DOCUMENTO FUE CARGADO SIN LAS FIRMAS DE GERENCIA NI SPCP</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260511140320</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -548,7 +548,6 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +609,6 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +670,6 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,7 +731,6 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,7 +792,6 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -860,7 +855,6 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -924,7 +918,6 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -988,7 +981,6 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1054,7 +1046,6 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1120,7 +1111,6 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1186,7 +1176,6 @@
           <t>ID_20260508075309</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1252,7 +1241,6 @@
           <t>ID_20260511140320</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,7 +1241,72 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>019303</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SPCP DANIEL GARCIA</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>EL NRO CONTROL CORRECTO ES: 00067903</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260512095527</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -547,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -608,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -669,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -730,6 +734,7 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,6 +796,7 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -854,6 +860,7 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -917,6 +924,7 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -980,6 +988,7 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1045,6 +1054,7 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1110,6 +1120,7 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1119,17 +1130,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INVERSIONES RUBYMAR R.M C.A</t>
+          <t>ADOLFO'S VICAR, C.A.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>008771</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1139,7 +1150,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SUB GERENTE DIANA BENAVIDES</t>
+          <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1154,7 +1165,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NO COLOCARON EL SELLO DE LA SUCURSAL</t>
+          <t>EL DOCUMENTO FUE CARGADO SIN LAS FIRMAS DE GERENCIA NI SPCP</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1172,9 +1183,10 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>ID_20260508075309</t>
-        </is>
-      </c>
+          <t>ID_20260511140320</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1184,17 +1196,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADOLFO'S VICAR, C.A.</t>
+          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>019303</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1204,12 +1216,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
+          <t>SPCP DANIEL GARCIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1219,7 +1231,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>EL DOCUMENTO FUE CARGADO SIN LAS FIRMAS DE GERENCIA NI SPCP</t>
+          <t>EL NRO CONTROL CORRECTO ES: 00067903</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1237,9 +1249,10 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ID_20260511140320</t>
-        </is>
-      </c>
+          <t>ID_20260512095527</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1249,17 +1262,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INVERSIONES AGROPECUARIA JEANDAVID, C.A.</t>
+          <t>INVERSIONES RUBYMAR R.M C.A</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>019303</t>
+          <t>008771</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1269,12 +1282,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SPCP DANIEL GARCIA</t>
+          <t>SUB GERENTE DIANA BENAVIDES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1284,7 +1297,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>EL NRO CONTROL CORRECTO ES: 00067903</t>
+          <t>NO COLOCARON EL SELLO DE LA SUCURSAL</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1302,11 +1315,16 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>ID_20260512095527</t>
+          <t>ID_20260508075309</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>INC_081416.webp</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -548,7 +548,6 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +609,6 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +670,6 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,7 +731,6 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,7 +792,6 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -860,7 +855,6 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -924,7 +918,6 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -988,7 +981,6 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1054,7 +1046,6 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1120,7 +1111,6 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1186,7 +1176,6 @@
           <t>ID_20260511140320</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1252,7 +1241,6 @@
           <t>ID_20260512095527</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,7 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,6 +610,7 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -670,6 +672,7 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -731,6 +734,7 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -792,6 +796,7 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -855,6 +860,7 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -918,6 +924,7 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -981,6 +988,7 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1046,6 +1054,7 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1111,6 +1120,7 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1176,6 +1186,7 @@
           <t>ID_20260511140320</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1241,6 +1252,7 @@
           <t>ID_20260512095527</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1311,6 +1323,72 @@
           <t>INC_081416.webp</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>INVERSIONES VELANDRIA, C.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> D007374</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GERENTE LOURDES PALACIOS</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NO FISCALIZÓ UNO O VARIOS PRODUCTOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AGREGARON EL SKU DE AJO PELADO 1KG Y ERA AJO PELADO DE 150GR </t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ID_20260513102702</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -548,7 +548,6 @@
       <c r="M2" t="n">
         <v>20260504090310</v>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,7 +609,6 @@
       <c r="M3" t="n">
         <v>20260504130707</v>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -672,7 +670,6 @@
       <c r="M4" t="n">
         <v>20260504131139</v>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -734,7 +731,6 @@
       <c r="M5" t="n">
         <v>20260504133240</v>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -796,7 +792,6 @@
       <c r="M6" t="n">
         <v>20260504091556</v>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -860,7 +855,6 @@
           <t>ID_20260505090942</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -924,7 +918,6 @@
           <t>ID_20260505093148</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -988,7 +981,6 @@
           <t>ID_20260505162358</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1054,7 +1046,6 @@
           <t>ID_20260506105909</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1120,7 +1111,6 @@
           <t>ID_20260506162828</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1186,7 +1176,6 @@
           <t>ID_20260511140320</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1252,7 +1241,6 @@
           <t>ID_20260512095527</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1388,7 +1376,6 @@
           <t>ID_20260513102702</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/ACACIAS.xlsx
+++ b/cuadros/MAYO/ACACIAS.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,8 +498,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>124694</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>124694</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -560,8 +561,10 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>848</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -621,8 +624,10 @@
           <t>MUSACEUM C.A</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>41178</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>41178</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -682,8 +687,10 @@
           <t>BOCADOS Y SABORES INTERNACIONALES, C.A.</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>31336</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>31336</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -743,8 +750,10 @@
           <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>24717</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>24717</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -804,8 +813,10 @@
           <t>YEFFERSON MAY MORGADO CHACON</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>32103</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>32103</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -867,8 +878,10 @@
           <t>DISTRIBUIDORA JORIAN,C.A</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>32098</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>32098</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -930,8 +943,10 @@
           <t>SERVICIOS SEPORVEN, C.A.</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>3088</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3088</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1377,7 +1392,207 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EMBOTELLADORA CRISTAL C.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1009132</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ESTOS PRODUCTOS NO PERTENECEN A LA RECEPCION ELIMINAR : BEB0511, BEB0528 Y BEB0221</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ID_20260514155030</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH C.A.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 025594</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SUB GERENTE SANTOS MOLINA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AGREGARON EL RUBRO AJO PELADO 2 VECES, ELIMINAR UNA Y AGREGAR EL RUBRO AJO PORRO EL CUAL FUE EL PRODUCTO RECIBIDO</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>ID_20260515093055</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ACACIAS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>QUESERA Y CHARCUTERIA CAMILA C.A.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>31297</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPCP AIRONDIC JIMENEZ </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FALTO COLOCAR EL SELLO DE LA SUCURSAL EN EL DOCUMENTO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>ID_20260515132148</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>INC_132148_0.jpeg INC_132148_1.jpeg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>